--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -935,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122209014</v>
+        <v>122209017</v>
       </c>
       <c r="B4" t="n">
         <v>102257</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369046</v>
+        <v>369002</v>
       </c>
       <c r="R4" t="n">
-        <v>6246459</v>
+        <v>6246458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122209013</v>
+        <v>122209014</v>
       </c>
       <c r="B5" t="n">
         <v>102257</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369052</v>
+        <v>369046</v>
       </c>
       <c r="R5" t="n">
-        <v>6246438</v>
+        <v>6246459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122209017</v>
+        <v>122209013</v>
       </c>
       <c r="B6" t="n">
         <v>102257</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369002</v>
+        <v>369052</v>
       </c>
       <c r="R6" t="n">
-        <v>6246458</v>
+        <v>6246438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122209017</v>
+        <v>122209014</v>
       </c>
       <c r="B4" t="n">
-        <v>102257</v>
+        <v>102267</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369002</v>
+        <v>369046</v>
       </c>
       <c r="R4" t="n">
-        <v>6246458</v>
+        <v>6246459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122209014</v>
+        <v>122209013</v>
       </c>
       <c r="B5" t="n">
-        <v>102257</v>
+        <v>102267</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369046</v>
+        <v>369052</v>
       </c>
       <c r="R5" t="n">
-        <v>6246459</v>
+        <v>6246438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122209013</v>
+        <v>122209017</v>
       </c>
       <c r="B6" t="n">
-        <v>102257</v>
+        <v>102267</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369052</v>
+        <v>369002</v>
       </c>
       <c r="R6" t="n">
-        <v>6246438</v>
+        <v>6246458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -1046,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122209013</v>
+        <v>122209017</v>
       </c>
       <c r="B5" t="n">
         <v>102267</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369052</v>
+        <v>369002</v>
       </c>
       <c r="R5" t="n">
-        <v>6246438</v>
+        <v>6246458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122209017</v>
+        <v>122209013</v>
       </c>
       <c r="B6" t="n">
         <v>102267</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369002</v>
+        <v>369052</v>
       </c>
       <c r="R6" t="n">
-        <v>6246458</v>
+        <v>6246438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>122209014</v>
       </c>
       <c r="B4" t="n">
-        <v>102267</v>
+        <v>102280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>122209017</v>
       </c>
       <c r="B5" t="n">
-        <v>102267</v>
+        <v>102280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>122209013</v>
       </c>
       <c r="B6" t="n">
-        <v>102267</v>
+        <v>102280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>122209014</v>
       </c>
       <c r="B4" t="n">
-        <v>102280</v>
+        <v>102285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122209017</v>
+        <v>122209013</v>
       </c>
       <c r="B5" t="n">
-        <v>102280</v>
+        <v>102285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369002</v>
+        <v>369052</v>
       </c>
       <c r="R5" t="n">
-        <v>6246458</v>
+        <v>6246438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122209013</v>
+        <v>122209017</v>
       </c>
       <c r="B6" t="n">
-        <v>102280</v>
+        <v>102285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369052</v>
+        <v>369002</v>
       </c>
       <c r="R6" t="n">
-        <v>6246438</v>
+        <v>6246458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>122209014</v>
       </c>
       <c r="B4" t="n">
-        <v>102285</v>
+        <v>102294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,11 +952,6 @@
       </c>
       <c r="E4" t="n">
         <v>1403</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Skånebjörnbär</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1049,7 +1044,7 @@
         <v>122209013</v>
       </c>
       <c r="B5" t="n">
-        <v>102285</v>
+        <v>102294</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,11 +1058,6 @@
       </c>
       <c r="E5" t="n">
         <v>1403</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Skånebjörnbär</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1160,7 +1150,7 @@
         <v>122209017</v>
       </c>
       <c r="B6" t="n">
-        <v>102285</v>
+        <v>102294</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,11 +1164,6 @@
       </c>
       <c r="E6" t="n">
         <v>1403</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skånebjörnbär</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122209014</v>
+        <v>122209017</v>
       </c>
       <c r="B4" t="n">
-        <v>102294</v>
+        <v>102307</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,6 +953,11 @@
       <c r="E4" t="n">
         <v>1403</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skånebjörnbär</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Rubus axillaris</t>
@@ -965,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -979,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369046</v>
+        <v>369002</v>
       </c>
       <c r="R4" t="n">
-        <v>6246459</v>
+        <v>6246458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1044,7 +1049,7 @@
         <v>122209013</v>
       </c>
       <c r="B5" t="n">
-        <v>102294</v>
+        <v>102307</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,6 +1063,11 @@
       </c>
       <c r="E5" t="n">
         <v>1403</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skånebjörnbär</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1147,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122209017</v>
+        <v>122209014</v>
       </c>
       <c r="B6" t="n">
-        <v>102294</v>
+        <v>102307</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,6 +1175,11 @@
       <c r="E6" t="n">
         <v>1403</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skånebjörnbär</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Rubus axillaris</t>
@@ -1177,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1191,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369002</v>
+        <v>369046</v>
       </c>
       <c r="R6" t="n">
-        <v>6246458</v>
+        <v>6246459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122209017</v>
+        <v>122209014</v>
       </c>
       <c r="B4" t="n">
-        <v>102307</v>
+        <v>102320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369002</v>
+        <v>369046</v>
       </c>
       <c r="R4" t="n">
-        <v>6246458</v>
+        <v>6246459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122209013</v>
+        <v>122209017</v>
       </c>
       <c r="B5" t="n">
-        <v>102307</v>
+        <v>102320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>369052</v>
+        <v>369002</v>
       </c>
       <c r="R5" t="n">
-        <v>6246438</v>
+        <v>6246458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122209014</v>
+        <v>122209013</v>
       </c>
       <c r="B6" t="n">
-        <v>102307</v>
+        <v>102320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369046</v>
+        <v>369052</v>
       </c>
       <c r="R6" t="n">
-        <v>6246459</v>
+        <v>6246438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 48597-2019 artfynd.xlsx
+++ b/artfynd/A 48597-2019 artfynd.xlsx
@@ -935,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122209014</v>
+        <v>122209013</v>
       </c>
       <c r="B4" t="n">
         <v>102320</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369046</v>
+        <v>369052</v>
       </c>
       <c r="R4" t="n">
-        <v>6246459</v>
+        <v>6246438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122209013</v>
+        <v>122209014</v>
       </c>
       <c r="B6" t="n">
         <v>102320</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>369052</v>
+        <v>369046</v>
       </c>
       <c r="R6" t="n">
-        <v>6246438</v>
+        <v>6246459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
